--- a/artfynd/A 1775-2025 artfynd.xlsx
+++ b/artfynd/A 1775-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122435444</v>
       </c>
       <c r="B2" t="n">
-        <v>57744</v>
+        <v>57749</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 1775-2025 artfynd.xlsx
+++ b/artfynd/A 1775-2025 artfynd.xlsx
@@ -782,7 +782,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 1775-2025 artfynd.xlsx
+++ b/artfynd/A 1775-2025 artfynd.xlsx
@@ -693,11 +693,6 @@
       <c r="E2" t="n">
         <v>103015</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Regulus regulus</t>
@@ -782,7 +777,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 1775-2025 artfynd.xlsx
+++ b/artfynd/A 1775-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122435444</v>
       </c>
       <c r="B2" t="n">
-        <v>57749</v>
+        <v>57753</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>103015</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>

--- a/artfynd/A 1775-2025 artfynd.xlsx
+++ b/artfynd/A 1775-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122435444</v>
       </c>
       <c r="B2" t="n">
-        <v>57753</v>
+        <v>57754</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 1775-2025 artfynd.xlsx
+++ b/artfynd/A 1775-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122435444</v>
       </c>
       <c r="B2" t="n">
-        <v>57754</v>
+        <v>57848</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 1775-2025 artfynd.xlsx
+++ b/artfynd/A 1775-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,62 +675,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122435444</v>
+        <v>122436147</v>
       </c>
       <c r="B2" t="n">
-        <v>57848</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 1775, Svartgöl, Sm</t>
+          <t>Öndal-Svartgöl_A 1775-2025, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590121</v>
+        <v>590138</v>
       </c>
       <c r="R2" t="n">
-        <v>6441005</v>
+        <v>6440914</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -771,21 +765,131 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>122435444</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>A 1775, Svartgöl, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>590121</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6441005</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ukna</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Magnus Kasselstrand</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
